--- a/Excel/3_5_Enteric_Swine_WIP_v02.xlsx
+++ b/Excel/3_5_Enteric_Swine_WIP_v02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92456BE4-F994-42AA-B62B-D1785BC62230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EE2DEB-7752-4311-96B0-FD88F06BCACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="585" yWindow="495" windowWidth="37785" windowHeight="19140" activeTab="3" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1965" yWindow="780" windowWidth="36060" windowHeight="19710" activeTab="5" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="3.5.1.1-2 Enteric Methane" sheetId="69" r:id="rId6"/>
     <sheet name="Constants - Swine" sheetId="79" r:id="rId7"/>
     <sheet name="Constants - Common" sheetId="115" r:id="rId8"/>
-    <sheet name="Constants - Livestock" sheetId="43" r:id="rId9"/>
+    <sheet name="Constants - Common livestock" sheetId="43" r:id="rId9"/>
     <sheet name="Acknowledgements" sheetId="72" r:id="rId10"/>
   </sheets>
   <definedNames>
@@ -647,11 +647,9 @@
     <definedName name="X_Cell_Site_FarmName">'Input - Site'!$E$7</definedName>
     <definedName name="X_Cell_Site_ReportingEntityName">'Input - Site'!$E$8</definedName>
     <definedName name="X_Cell_Site_StartDate">'Input - Site'!$E$12</definedName>
+    <definedName name="X_Table_Swine_FeedIntake_Method1">'Input - Swine'!$D$12:$H$13</definedName>
+    <definedName name="X_Table_Swine_FeedIntake_Method2">'Input - Swine'!$D$15:$H$16</definedName>
     <definedName name="X_Table_Swine_HerdMovement">'Input - Swine'!$D$5:$H$7</definedName>
-    <definedName name="X_Table_Swine_ManureProduction_Method1">'Input - Swine'!$D$11:$H$12</definedName>
-    <definedName name="X_Table_Swine_ManureProduction_Method2">'Input - Swine'!$D$14:$H$15</definedName>
-    <definedName name="X_Table_Swine_VolatileSolidProduction_Method1">'Input - Swine'!$D$11:$H$12</definedName>
-    <definedName name="X_Table_Swine_VolatileSolidProduction_Method2">'Input - Swine'!$D$14:$H$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -711,7 +709,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="226">
   <si>
     <t>INPUTS</t>
   </si>
@@ -917,9 +915,6 @@
     <t>Constants - Common</t>
   </si>
   <si>
-    <t>Constants - Livestock</t>
-  </si>
-  <si>
     <t>Symbol</t>
   </si>
   <si>
@@ -1071,9 +1066,6 @@
   </si>
   <si>
     <t>Gilts</t>
-  </si>
-  <si>
-    <t>Volatile solids produced per head per day</t>
   </si>
   <si>
     <t>Class</t>
@@ -1281,9 +1273,6 @@
     <t>Feed intake (Method 2)</t>
   </si>
   <si>
-    <t>Manure production</t>
-  </si>
-  <si>
     <t>Home</t>
   </si>
   <si>
@@ -1432,6 +1421,21 @@
   </si>
   <si>
     <t>Acknowledgements</t>
+  </si>
+  <si>
+    <t>Livestock classes</t>
+  </si>
+  <si>
+    <t>Table_LivestockClasses_Swine</t>
+  </si>
+  <si>
+    <t>Livestock class</t>
+  </si>
+  <si>
+    <t>Constants - Common livestock</t>
+  </si>
+  <si>
+    <t>Feed intake</t>
   </si>
 </sst>
 </file>
@@ -2396,7 +2400,7 @@
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="4" borderId="0" xfId="8">
       <alignment horizontal="left" vertical="center"/>
@@ -2503,9 +2507,6 @@
     </xf>
     <xf numFmtId="4" fontId="25" fillId="0" borderId="0" xfId="18" applyFont="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="4" borderId="0" xfId="50">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6407,6 +6408,16 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E1B2F077-B50E-496E-9D04-990A6DB886BC}" name="Table_LivestockClasses_Swine" displayName="Table_LivestockClasses_Swine" ref="I8:I12" totalsRowShown="0">
+  <autoFilter ref="I8:I12" xr:uid="{E1B2F077-B50E-496E-9D04-990A6DB886BC}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{4D8C32DC-F5B0-420B-901A-933DB9711005}" name="Livestock class"/>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="30" xr:uid="{619E590C-B431-4360-99F7-BF15688E9D94}" name="Table_AustralianStates" displayName="Table_AustralianStates" ref="D6:F14" totalsRowShown="0">
   <autoFilter ref="D6:F14" xr:uid="{E0906749-7FC7-47DE-82F6-F796C4463018}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6428,7 +6439,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="31" xr:uid="{906B601D-1C01-4B46-893E-AAA2757149D6}" name="Table_WASA4Areas" displayName="Table_WASA4Areas" ref="D20:D30" totalsRowShown="0">
   <autoFilter ref="D20:D30" xr:uid="{5FA81339-C6C8-4D36-BEEA-6C4AEDD9E676}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6442,7 +6453,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="32" xr:uid="{A833C116-03AC-44ED-AA0D-1B08F41554EF}" name="Table_GWPData" displayName="Table_GWPData" ref="D36:E43" totalsRowShown="0">
   <autoFilter ref="D36:E43" xr:uid="{B8E87A66-3E41-4AD3-925D-01EE21B43D7A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6460,7 +6471,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="33" xr:uid="{0C65D20E-8BF4-4C9C-92BE-A45A33A51092}" name="Table_GasToMolecularConversionFactor" displayName="Table_GasToMolecularConversionFactor" ref="D47:H54" totalsRowShown="0">
   <autoFilter ref="D47:H54" xr:uid="{C1F562BB-DAA6-45BB-951A-7BAFA5B64B45}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6490,7 +6501,57 @@
 </table>
 </file>
 
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8BFD9E79-6224-4B04-B002-84DC46086DAC}" name="Table_SourceData_Swine_MMSMCF" displayName="Table_SourceData_Swine_MMSMCF" ref="D28:M35" totalsRowShown="0">
+  <autoFilter ref="D28:M35" xr:uid="{8BFD9E79-6224-4B04-B002-84DC46086DAC}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{948C8C81-0F25-4404-945E-CD16BE93BFBF}" name="MMS">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{CC6F19AB-67BC-413A-9108-447CB795CC02}" name="NSW" dataDxfId="79" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{EFE4C41A-233A-4E7D-912F-E949B7110A0A}" name="ACT" dataDxfId="78" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{90D72B45-949A-49D4-8B76-EF78C1A193C9}" name="QLD" dataDxfId="77" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{D7D725B2-0CF9-4EB2-A5C1-09EDA961537A}" name="NT" dataDxfId="76" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{2934DF60-275E-438D-A730-DD780A8931E8}" name="SA" dataDxfId="75" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{29BE3DB6-3057-4DB9-9C8B-816C15103256}" name="TAS" dataDxfId="74" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{FF50759B-240C-4451-AB1C-3143673818F2}" name="VIC" dataDxfId="73" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{F164F2B6-4BA2-43CA-8A29-E52D5447FFC0}" name="WA" dataDxfId="72" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{F171BCD0-98D2-4E5E-AC27-147712A91756}" name="NIR definition" dataDxfId="71" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="34" xr:uid="{2B474A35-BC89-4677-813E-B391DB5A2FB4}" name="Table_SourceData_ClimateZones" displayName="Table_SourceData_ClimateZones" ref="D89:S97" totalsRowShown="0">
   <autoFilter ref="D89:S97" xr:uid="{5A437AE9-7724-4CF2-ACCF-291078682FB9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6564,57 +6625,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8BFD9E79-6224-4B04-B002-84DC46086DAC}" name="Table_SourceData_Swine_MMSMCF" displayName="Table_SourceData_Swine_MMSMCF" ref="D28:M35" totalsRowShown="0">
-  <autoFilter ref="D28:M35" xr:uid="{8BFD9E79-6224-4B04-B002-84DC46086DAC}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-    <filterColumn colId="9" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{948C8C81-0F25-4404-945E-CD16BE93BFBF}" name="MMS">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{CC6F19AB-67BC-413A-9108-447CB795CC02}" name="NSW" dataDxfId="79" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{EFE4C41A-233A-4E7D-912F-E949B7110A0A}" name="ACT" dataDxfId="78" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{90D72B45-949A-49D4-8B76-EF78C1A193C9}" name="QLD" dataDxfId="77" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="5" xr3:uid="{D7D725B2-0CF9-4EB2-A5C1-09EDA961537A}" name="NT" dataDxfId="76" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="6" xr3:uid="{2934DF60-275E-438D-A730-DD780A8931E8}" name="SA" dataDxfId="75" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{29BE3DB6-3057-4DB9-9C8B-816C15103256}" name="TAS" dataDxfId="74" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="8" xr3:uid="{FF50759B-240C-4451-AB1C-3143673818F2}" name="VIC" dataDxfId="73" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="9" xr3:uid="{F164F2B6-4BA2-43CA-8A29-E52D5447FFC0}" name="WA" dataDxfId="72" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{F171BCD0-98D2-4E5E-AC27-147712A91756}" name="NIR definition" dataDxfId="71" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(SourceData_Swine.SourceData_Swine_MMS_MCFs_Data(),Table_SourceData_Swine_MMSMCF[[#Headers],[MMS]],0)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="35" xr:uid="{CFC4EA38-AEDC-4047-BDE3-850527C07CAD}" name="Table_SourceData_WetDryZones" displayName="Table_SourceData_WetDryZones" ref="D63:E77" totalsRowShown="0">
   <autoFilter ref="D63:E77" xr:uid="{3597E019-B21E-4B76-BCC8-D02D497BCFA9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6632,7 +6643,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="36" xr:uid="{C89320BE-DFD9-4F66-A4C0-CBBED12446B7}" name="Table_SourceData_TemperatureZones" displayName="Table_SourceData_TemperatureZones" ref="D109:G112" totalsRowShown="0">
   <autoFilter ref="D109:G112" xr:uid="{AB16FEAB-AB03-45E1-BBD4-66D29CD412DF}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6658,7 +6669,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="37" xr:uid="{11CA7512-AAB1-4F94-B403-0FE499B7B427}" name="Table_SourceData_RainfallZones" displayName="Table_SourceData_RainfallZones" ref="D119:G121" totalsRowShown="0">
   <autoFilter ref="D119:G121" xr:uid="{E08772F3-2E8C-40A8-B755-08A5BBDF4130}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6684,7 +6695,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="38" xr:uid="{F5E04D3F-E92D-44EC-BC47-56D9FB155491}" name="Table_SourceData_LeachingZones" displayName="Table_SourceData_LeachingZones" ref="D127:E129" totalsRowShown="0">
   <autoFilter ref="D127:E129" xr:uid="{A159E140-02ED-4547-B6E1-6695D8B16A11}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6702,7 +6713,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="39" xr:uid="{4F884470-4BC9-45DC-B3BF-58E560F3290D}" name="Table_SourceData_DataScores_Scope3" displayName="Table_SourceData_DataScores_Scope3" ref="D153:E158" totalsRowShown="0">
   <autoFilter ref="D153:E158" xr:uid="{133D42B0-F6D2-470A-858A-37E6A7F5EC2B}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6720,7 +6731,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="40" xr:uid="{90236E93-300B-42C2-8EB7-E26A4C3A462D}" name="Table_SourceData_FracWET" displayName="Table_SourceData_FracWET" ref="D134:E136" totalsRowShown="0">
   <autoFilter ref="D134:E136" xr:uid="{308E99BE-FE1F-47A4-B2CA-97217277C4E9}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6738,7 +6749,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="41" xr:uid="{466D624A-6262-4B79-8B4E-85188CACABEE}" name="Table_SourceData_Common_EFN2O" displayName="Table_SourceData_Common_EFN2O" ref="D186:H199" totalsRowShown="0">
   <autoFilter ref="D186:H199" xr:uid="{D41FBEA4-8379-4DF7-A068-BF94D364F1A2}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6768,7 +6779,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="42" xr:uid="{97096799-EE45-4764-903D-631ADE9E3967}" name="Table_SourceData_FracWETIrrigation" displayName="Table_SourceData_FracWETIrrigation" ref="D142:E147" totalsRowShown="0">
   <autoFilter ref="D142:E147" xr:uid="{1F48CA34-50DE-46D5-B32A-BB3A1E818E37}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6786,7 +6797,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="43" xr:uid="{34E53EBB-DB8E-477E-9EBC-131BDE06B8A6}" name="Table_SourceData_EFPastureRangeAndPaddock" displayName="Table_SourceData_EFPastureRangeAndPaddock" ref="D206:E208" totalsRowShown="0">
   <autoFilter ref="D206:E208" xr:uid="{D5BE3F89-D70E-4C53-A71C-E756622DEF38}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6798,24 +6809,6 @@
     </tableColumn>
     <tableColumn id="2" xr3:uid="{7A26D427-C856-4145-9747-F08CCA41A6F5}" name="EFPRP" dataDxfId="39" dataCellStyle="Content normal">
       <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{8734AA79-CB5F-4195-A7C8-C38C459AB000}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
-  <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{4489322D-5AE6-40C1-BEED-B2944D80F65F}" name="Month">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{1213DFA2-5F54-4F6A-911F-1A1A0FF066AC}" name="Season" dataDxfId="38" dataCellStyle="Content normal">
-      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -6837,6 +6830,24 @@
 </file>
 
 <file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="44" xr:uid="{8734AA79-CB5F-4195-A7C8-C38C459AB000}" name="Table_SourceData_Common_MonthToSeason" displayName="Table_SourceData_Common_MonthToSeason" ref="D212:E224" totalsRowShown="0">
+  <autoFilter ref="D212:E224" xr:uid="{97796C3A-D95E-4077-AA20-A8FE4145DAAD}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{4489322D-5AE6-40C1-BEED-B2944D80F65F}" name="Month">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{1213DFA2-5F54-4F6A-911F-1A1A0FF066AC}" name="Season" dataDxfId="38" dataCellStyle="Content normal">
+      <calculatedColumnFormula array="1">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Equation table" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="45" xr:uid="{CE9E1C79-2A76-4C8A-AE27-F309F6C012C8}" name="Table_SourceData_Common_MCFTemperatureZone" displayName="Table_SourceData_Common_MCFTemperatureZone" ref="D231:S250" totalsRowShown="0">
   <autoFilter ref="D231:S250" xr:uid="{1D72DD9B-C8FA-48F4-9A11-20231FF87B5A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6910,7 +6921,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="49" xr:uid="{05857664-B945-44AE-92EB-650E8DF751CC}" name="Table_SourceData_Common_EFOrganicFertCropResidues" displayName="Table_SourceData_Common_EFOrganicFertCropResidues" ref="D257:E259" totalsRowShown="0">
   <autoFilter ref="D257:E259" xr:uid="{56E01C14-1BB8-4015-9158-4CEB4D3B605C}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6928,7 +6939,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="54" xr:uid="{9328F4F5-6389-439B-A713-4FF69664D925}" name="Table_SourceData_DataQuality_TemporalRepresentativeness" displayName="Table_SourceData_DataQuality_TemporalRepresentativeness" ref="D265:F270" totalsRowShown="0">
   <autoFilter ref="D265:F270" xr:uid="{9AD44602-D2F2-4D97-923C-A32E98F8C17A}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6944,7 +6955,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="55" xr:uid="{AE33C005-3283-4276-9189-7F266A9669D0}" name="Table_SourceData_DataQuality_SpatialRepresentativeness" displayName="Table_SourceData_DataQuality_SpatialRepresentativeness" ref="D274:F279" totalsRowShown="0">
   <autoFilter ref="D274:F279" xr:uid="{95094D65-3E0E-45CE-A3F4-F41E74C11901}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6960,7 +6971,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="56" xr:uid="{A6BABD70-79D6-4461-B03B-663070A4C31E}" name="Table_SourceData_DataQuality_SampleSize" displayName="Table_SourceData_DataQuality_SampleSize" ref="D283:F288" totalsRowShown="0">
   <autoFilter ref="D283:F288" xr:uid="{DE8F748C-E65A-4AA2-81BB-D28A432CF334}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6976,7 +6987,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="57" xr:uid="{B014B341-1916-466B-87AC-85890E9EC0AA}" name="Table_SourceData_DataQuality_Scope3" displayName="Table_SourceData_DataQuality_Scope3" ref="D292:F297" totalsRowShown="0">
   <autoFilter ref="D292:F297" xr:uid="{43A1C4DA-75D1-45DF-BA9A-1798C2CC5A4B}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -6992,7 +7003,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table37.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}" name="Table_Data_MMSSymbols" displayName="Table_Data_MMSSymbols" ref="D9:F27" totalsRowShown="0">
   <autoFilter ref="D9:F27" xr:uid="{757CC28B-CF78-4195-86CA-5AEBBA7FA04E}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -7377,17 +7388,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="122" t="str">
+      <c r="A3" s="121" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="121" t="s">
+      <c r="A6" s="120" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7418,7 +7429,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
@@ -7428,7 +7439,7 @@
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="121" t="s">
+      <c r="A6" s="120" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7439,7 +7450,7 @@
       </c>
     </row>
     <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="120" t="str">
+      <c r="A8" s="119" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
       </c>
@@ -7466,20 +7477,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="e" vm="1">
+      <c r="A1" s="58" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="116" t="s">
-        <v>164</v>
-      </c>
-      <c r="D1" s="116"/>
-      <c r="E1" s="116"/>
-      <c r="F1" s="116"/>
-      <c r="G1" s="116"/>
-      <c r="H1" s="116"/>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
+      <c r="C1" s="115" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" s="115"/>
+      <c r="E1" s="115"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2"/>
@@ -7497,18 +7508,18 @@
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="K3" s="114"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
+      <c r="H3" s="113"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="113"/>
+      <c r="K3" s="113"/>
     </row>
     <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="117" t="str">
+      <c r="A4" s="116" t="str">
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
@@ -7518,24 +7529,24 @@
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
-      <c r="D5" s="104" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="77"/>
+      <c r="D5" s="103" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="76"/>
     </row>
     <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="115" t="s">
-        <v>166</v>
-      </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="78"/>
+      <c r="D6" s="114" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="77"/>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7571,7 +7582,7 @@
     <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="120" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7589,8 +7600,8 @@
     </row>
     <row r="20" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
-        <v>Constants - Livestock</v>
+        <f>HYPERLINK("#'Constants - Common livestock'!A1", "Constants - Common livestock")</f>
+        <v>Constants - Common livestock</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7650,11 +7661,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="e" vm="1">
+      <c r="A1" s="58" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="97" t="s">
-        <v>163</v>
+      <c r="C1" s="96" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7693,7 +7704,7 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="117" t="str">
+      <c r="A5" s="116" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
@@ -7709,55 +7720,55 @@
     </row>
     <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="20"/>
-      <c r="D6" s="96" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="96" t="s">
+      <c r="D6" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="95" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="95" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="96" t="s">
+      <c r="G6" s="95" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="96" t="s">
+      <c r="I6" s="95" t="s">
+        <v>99</v>
+      </c>
+      <c r="J6" s="95" t="s">
         <v>89</v>
-      </c>
-      <c r="H6" s="96" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" s="96" t="s">
-        <v>100</v>
-      </c>
-      <c r="J6" s="96" t="s">
-        <v>90</v>
       </c>
       <c r="K6" s="20"/>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="20"/>
       <c r="D7" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="105">
+        <v>155</v>
+      </c>
+      <c r="E7" s="104">
         <f ca="1">VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method1</f>
         <v>0.78573884462151411</v>
       </c>
-      <c r="F7" s="105">
+      <c r="F7" s="104">
         <f ca="1">VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method2</f>
         <v>0.78573884462151411</v>
       </c>
-      <c r="G7" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="93">
+      <c r="G7" s="46" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="92">
         <f ca="1">'3.5.1.1-2 Enteric Methane'!E63</f>
         <v>22.000687649402394</v>
       </c>
-      <c r="I7" s="93">
+      <c r="I7" s="92">
         <f ca="1">'3.5.1.1-2 Enteric Methane'!N63</f>
         <v>22.000687649402394</v>
       </c>
-      <c r="J7" s="47" t="s">
-        <v>95</v>
+      <c r="J7" s="46" t="s">
+        <v>94</v>
       </c>
       <c r="K7" s="20"/>
     </row>
@@ -7767,21 +7778,21 @@
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="21"/>
       <c r="G8" s="27"/>
-      <c r="H8" s="95">
+      <c r="H8" s="94">
         <f ca="1">SUM(H7:H7)</f>
         <v>22.000687649402394</v>
       </c>
-      <c r="I8" s="95">
+      <c r="I8" s="94">
         <f ca="1">SUM(I7:I7)</f>
         <v>22.000687649402394</v>
       </c>
-      <c r="J8" s="89" t="s">
-        <v>95</v>
+      <c r="J8" s="88" t="s">
+        <v>94</v>
       </c>
       <c r="K8" s="20"/>
     </row>
@@ -7889,7 +7900,7 @@
       <c r="K16" s="20"/>
     </row>
     <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="120" t="s">
         <v>1</v>
       </c>
       <c r="C17" s="20"/>
@@ -7934,8 +7945,8 @@
     </row>
     <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
-        <v>Constants - Livestock</v>
+        <f>HYPERLINK("#'Constants - Common livestock'!A1", "Constants - Common livestock")</f>
+        <v>Constants - Common livestock</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="1"/>
@@ -8145,8 +8156,8 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="92"/>
-      <c r="J38" s="92"/>
+      <c r="I38" s="91"/>
+      <c r="J38" s="91"/>
       <c r="K38" s="20"/>
     </row>
     <row r="39" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8156,8 +8167,8 @@
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="92"/>
-      <c r="J39" s="92"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="91"/>
       <c r="K39" s="20"/>
     </row>
     <row r="40" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8167,8 +8178,8 @@
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
+      <c r="I40" s="91"/>
+      <c r="J40" s="91"/>
       <c r="K40" s="20"/>
     </row>
     <row r="41" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8178,8 +8189,8 @@
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
+      <c r="I41" s="91"/>
+      <c r="J41" s="91"/>
       <c r="K41" s="20"/>
     </row>
     <row r="42" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8189,8 +8200,8 @@
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="92"/>
-      <c r="J42" s="92"/>
+      <c r="I42" s="91"/>
+      <c r="J42" s="91"/>
       <c r="K42" s="20"/>
     </row>
     <row r="43" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8200,8 +8211,8 @@
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
-      <c r="I43" s="92"/>
-      <c r="J43" s="92"/>
+      <c r="I43" s="91"/>
+      <c r="J43" s="91"/>
       <c r="K43" s="20"/>
     </row>
     <row r="44" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8211,8 +8222,8 @@
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
-      <c r="I44" s="92"/>
-      <c r="J44" s="92"/>
+      <c r="I44" s="91"/>
+      <c r="J44" s="91"/>
       <c r="K44" s="20"/>
     </row>
     <row r="45" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8222,8 +8233,8 @@
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="92"/>
-      <c r="J45" s="92"/>
+      <c r="I45" s="91"/>
+      <c r="J45" s="91"/>
       <c r="K45" s="20"/>
     </row>
     <row r="46" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8233,8 +8244,8 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
-      <c r="I46" s="92"/>
-      <c r="J46" s="92"/>
+      <c r="I46" s="91"/>
+      <c r="J46" s="91"/>
       <c r="K46" s="20"/>
     </row>
     <row r="47" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8244,8 +8255,8 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-      <c r="I47" s="92"/>
-      <c r="J47" s="92"/>
+      <c r="I47" s="91"/>
+      <c r="J47" s="91"/>
       <c r="K47" s="20"/>
     </row>
     <row r="48" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8255,8 +8266,8 @@
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="92"/>
-      <c r="J48" s="92"/>
+      <c r="I48" s="91"/>
+      <c r="J48" s="91"/>
       <c r="K48" s="20"/>
     </row>
     <row r="49" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8265,9 +8276,9 @@
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="H49" s="92"/>
-      <c r="I49" s="92"/>
-      <c r="J49" s="92"/>
+      <c r="H49" s="91"/>
+      <c r="I49" s="91"/>
+      <c r="J49" s="91"/>
       <c r="K49" s="20"/>
     </row>
     <row r="50" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8276,9 +8287,9 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
-      <c r="H50" s="92"/>
-      <c r="I50" s="92"/>
-      <c r="J50" s="92"/>
+      <c r="H50" s="91"/>
+      <c r="I50" s="91"/>
+      <c r="J50" s="91"/>
       <c r="K50" s="20"/>
     </row>
     <row r="51" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8287,9 +8298,9 @@
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="H51" s="92"/>
-      <c r="I51" s="92"/>
-      <c r="J51" s="92"/>
+      <c r="H51" s="91"/>
+      <c r="I51" s="91"/>
+      <c r="J51" s="91"/>
       <c r="K51" s="20"/>
     </row>
     <row r="52" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8298,9 +8309,9 @@
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
-      <c r="H52" s="92"/>
-      <c r="I52" s="92"/>
-      <c r="J52" s="92"/>
+      <c r="H52" s="91"/>
+      <c r="I52" s="91"/>
+      <c r="J52" s="91"/>
       <c r="K52" s="20"/>
     </row>
     <row r="53" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8309,9 +8320,9 @@
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
-      <c r="H53" s="92"/>
-      <c r="I53" s="92"/>
-      <c r="J53" s="92"/>
+      <c r="H53" s="91"/>
+      <c r="I53" s="91"/>
+      <c r="J53" s="91"/>
       <c r="K53" s="20"/>
     </row>
     <row r="54" spans="3:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8715,11 +8726,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="e" vm="1">
+      <c r="A1" s="58" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:24" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8765,15 +8776,15 @@
         <f>HYPERLINK("#'Overview'!A1", "Overview")</f>
         <v>Overview</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
@@ -8812,7 +8823,7 @@
       </c>
     </row>
     <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="118" t="str">
+      <c r="A9" s="117" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
@@ -8823,12 +8834,12 @@
         <f>HYPERLINK("#'Input - Swine'!A1", "Swine")</f>
         <v>Swine</v>
       </c>
-      <c r="D10" s="83" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="82"/>
-      <c r="F10" s="84"/>
-      <c r="G10" s="79"/>
+      <c r="D10" s="82" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" s="81"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="78"/>
       <c r="N10" s="37"/>
     </row>
     <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8838,9 +8849,9 @@
     <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="E12" s="57">
+        <v>70</v>
+      </c>
+      <c r="E12" s="56">
         <v>45292</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -8852,9 +8863,9 @@
         <v>54</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="61">
+        <v>71</v>
+      </c>
+      <c r="E13" s="60">
         <f>DATE(YEAR(X_Cell_Site_StartDate)+1,MONTH(X_Cell_Site_StartDate),DAY(X_Cell_Site_StartDate))-1</f>
         <v>45657</v>
       </c>
@@ -8888,7 +8899,7 @@
       <c r="O16" s="34"/>
     </row>
     <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="120" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="1"/>
@@ -8922,8 +8933,8 @@
     </row>
     <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
-        <v>Constants - Livestock</v>
+        <f>HYPERLINK("#'Constants - Common livestock'!A1", "Constants - Common livestock")</f>
+        <v>Constants - Common livestock</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -9015,20 +9026,20 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="42"/>
-      <c r="V30" s="42"/>
-      <c r="W30" s="42"/>
-      <c r="X30" s="42"/>
-      <c r="Y30" s="42"/>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="41"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="41"/>
+      <c r="S30" s="41"/>
+      <c r="T30" s="41"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
+      <c r="W30" s="41"/>
+      <c r="X30" s="41"/>
+      <c r="Y30" s="41"/>
     </row>
     <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
@@ -9103,8 +9114,8 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="J34" s="54"/>
-      <c r="K34" s="64"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="63"/>
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
       <c r="N34" s="40"/>
@@ -9127,8 +9138,8 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="J35" s="54"/>
-      <c r="K35" s="64"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="63"/>
       <c r="L35" s="40"/>
       <c r="M35" s="40"/>
       <c r="N35" s="40"/>
@@ -9146,14 +9157,14 @@
     </row>
     <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
-      <c r="D36" s="62"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="54"/>
-      <c r="K36" s="64"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="62"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="63"/>
       <c r="L36" s="40"/>
       <c r="M36" s="40"/>
       <c r="N36" s="40"/>
@@ -9171,14 +9182,14 @@
     </row>
     <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
-      <c r="D37" s="62"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="54"/>
-      <c r="H37" s="54"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="54"/>
-      <c r="K37" s="64"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="61"/>
+      <c r="F37" s="62"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="63"/>
       <c r="L37" s="40"/>
       <c r="M37" s="40"/>
       <c r="N37" s="40"/>
@@ -9196,14 +9207,14 @@
     </row>
     <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="54"/>
-      <c r="K38" s="64"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="61"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="63"/>
       <c r="L38" s="40"/>
       <c r="M38" s="40"/>
       <c r="N38" s="40"/>
@@ -9221,14 +9232,14 @@
     </row>
     <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="54"/>
-      <c r="H39" s="54"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="54"/>
-      <c r="K39" s="64"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="61"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="63"/>
       <c r="L39" s="40"/>
       <c r="M39" s="40"/>
       <c r="N39" s="40"/>
@@ -9246,28 +9257,28 @@
     </row>
     <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="43"/>
-      <c r="N40" s="43"/>
-      <c r="O40" s="43"/>
-      <c r="P40" s="43"/>
-      <c r="Q40" s="43"/>
-      <c r="R40" s="43"/>
-      <c r="S40" s="43"/>
-      <c r="T40" s="43"/>
-      <c r="U40" s="43"/>
-      <c r="V40" s="43"/>
-      <c r="W40" s="43"/>
-      <c r="X40" s="43"/>
-      <c r="Y40" s="43"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="65"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="66"/>
+      <c r="J40" s="66"/>
+      <c r="K40" s="66"/>
+      <c r="L40" s="42"/>
+      <c r="M40" s="42"/>
+      <c r="N40" s="42"/>
+      <c r="O40" s="42"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="42"/>
+      <c r="S40" s="42"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="42"/>
+      <c r="V40" s="42"/>
+      <c r="W40" s="42"/>
+      <c r="X40" s="42"/>
+      <c r="Y40" s="42"/>
     </row>
     <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
@@ -9291,11 +9302,11 @@
     </row>
     <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="68"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="67"/>
     </row>
     <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
@@ -9323,11 +9334,11 @@
     </row>
     <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
-      <c r="D51" s="69"/>
-      <c r="E51" s="70"/>
-      <c r="F51" s="70"/>
-      <c r="G51" s="70"/>
-      <c r="H51" s="71"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="69"/>
+      <c r="F51" s="69"/>
+      <c r="G51" s="69"/>
+      <c r="H51" s="70"/>
     </row>
     <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
@@ -9337,63 +9348,63 @@
     </row>
     <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
-      <c r="D54" s="74"/>
-      <c r="G54" s="72"/>
+      <c r="D54" s="73"/>
+      <c r="G54" s="71"/>
     </row>
     <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
-      <c r="D55" s="74"/>
+      <c r="D55" s="73"/>
     </row>
     <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
-      <c r="D56" s="74"/>
+      <c r="D56" s="73"/>
     </row>
     <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
-      <c r="D57" s="74"/>
-      <c r="F57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="F57" s="72"/>
     </row>
     <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
+      <c r="D58" s="73"/>
+      <c r="E58" s="73"/>
     </row>
     <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="73"/>
     </row>
     <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
-      <c r="D60" s="74"/>
-      <c r="E60" s="75"/>
+      <c r="D60" s="73"/>
+      <c r="E60" s="74"/>
     </row>
     <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
-      <c r="D61" s="74"/>
+      <c r="D61" s="73"/>
     </row>
     <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
-      <c r="D62" s="74"/>
+      <c r="D62" s="73"/>
     </row>
     <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
-      <c r="D63" s="74"/>
+      <c r="D63" s="73"/>
     </row>
     <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
-      <c r="D64" s="74"/>
-      <c r="E64" s="74"/>
+      <c r="D64" s="73"/>
+      <c r="E64" s="73"/>
     </row>
     <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
-      <c r="D65" s="74"/>
-      <c r="E65" s="74"/>
+      <c r="D65" s="73"/>
+      <c r="E65" s="73"/>
     </row>
     <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
-      <c r="D66" s="74"/>
-      <c r="E66" s="75"/>
+      <c r="D66" s="73"/>
+      <c r="E66" s="74"/>
     </row>
     <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
@@ -9403,39 +9414,39 @@
     </row>
     <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
-      <c r="D69" s="53"/>
-      <c r="E69" s="53"/>
-      <c r="F69" s="53"/>
-      <c r="G69" s="53"/>
-      <c r="H69" s="53"/>
-      <c r="I69" s="53"/>
+      <c r="D69" s="52"/>
+      <c r="E69" s="52"/>
+      <c r="F69" s="52"/>
+      <c r="G69" s="52"/>
+      <c r="H69" s="52"/>
+      <c r="I69" s="52"/>
     </row>
     <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
-      <c r="D70" s="53"/>
-      <c r="E70" s="53"/>
-      <c r="F70" s="53"/>
-      <c r="G70" s="53"/>
-      <c r="H70" s="53"/>
-      <c r="I70" s="53"/>
+      <c r="D70" s="52"/>
+      <c r="E70" s="52"/>
+      <c r="F70" s="52"/>
+      <c r="G70" s="52"/>
+      <c r="H70" s="52"/>
+      <c r="I70" s="52"/>
     </row>
     <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
-      <c r="D71" s="53"/>
-      <c r="E71" s="53"/>
-      <c r="F71" s="53"/>
-      <c r="G71" s="53"/>
-      <c r="H71" s="53"/>
-      <c r="I71" s="53"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
     </row>
     <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
-      <c r="D72" s="53"/>
-      <c r="E72" s="53"/>
-      <c r="F72" s="53"/>
-      <c r="G72" s="53"/>
-      <c r="H72" s="53"/>
-      <c r="I72" s="53"/>
+      <c r="D72" s="52"/>
+      <c r="E72" s="52"/>
+      <c r="F72" s="52"/>
+      <c r="G72" s="52"/>
+      <c r="H72" s="52"/>
+      <c r="I72" s="52"/>
     </row>
     <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
@@ -9454,23 +9465,23 @@
     </row>
     <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
-      <c r="D78" s="76"/>
+      <c r="D78" s="75"/>
     </row>
     <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
-      <c r="D79" s="76"/>
+      <c r="D79" s="75"/>
     </row>
     <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
-      <c r="D80" s="76"/>
+      <c r="D80" s="75"/>
     </row>
     <row r="81" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
-      <c r="D81" s="76"/>
+      <c r="D81" s="75"/>
     </row>
     <row r="82" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
-      <c r="D82" s="76"/>
+      <c r="D82" s="75"/>
     </row>
     <row r="83" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
@@ -9741,39 +9752,39 @@
     <col min="5" max="8" width="30.7109375" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.5703125" style="1" customWidth="1"/>
     <col min="10" max="10" width="4.7109375" style="1" customWidth="1"/>
-    <col min="11" max="12" width="4.7109375" style="49" customWidth="1"/>
-    <col min="13" max="18" width="30.7109375" style="49" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="49" customWidth="1"/>
+    <col min="11" max="12" width="4.7109375" style="48" customWidth="1"/>
+    <col min="13" max="18" width="30.7109375" style="48" customWidth="1"/>
+    <col min="19" max="19" width="4.7109375" style="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="59" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="e" vm="1">
+    <row r="1" spans="1:19" s="58" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="58" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C1" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
-      <c r="N1" s="49"/>
-      <c r="O1" s="49"/>
-      <c r="P1" s="49"/>
-      <c r="Q1" s="49"/>
-      <c r="R1" s="49"/>
-      <c r="S1" s="49"/>
+      <c r="C1" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="K1" s="48"/>
+      <c r="L1" s="48"/>
+      <c r="M1" s="48"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="48"/>
+      <c r="P1" s="48"/>
+      <c r="Q1" s="48"/>
+      <c r="R1" s="48"/>
+      <c r="S1" s="48"/>
     </row>
     <row r="2" spans="1:19" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="49"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="49"/>
-      <c r="S2" s="49"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
     </row>
     <row r="3" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
@@ -9800,36 +9811,36 @@
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
       </c>
-      <c r="E5" s="98" t="s">
+      <c r="E5" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="F5" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="F5" s="98" t="s">
+      <c r="G5" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="G5" s="98" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" s="98" t="s">
-        <v>127</v>
+      <c r="H5" s="97" t="s">
+        <v>125</v>
       </c>
       <c r="J5" s="3"/>
       <c r="N5" s="7"/>
     </row>
     <row r="6" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D6" s="41" t="str">
+      <c r="D6" s="1" t="str">
         <f>"Average duration of stay between " &amp; TEXT(X_Cell_Site_StartDate, "dd mmm yy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "dd mmm yy")</f>
         <v>Average duration of stay between 01 Jan 24 and 31 Dec 24</v>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="57">
         <v>365</v>
       </c>
-      <c r="F6" s="58">
+      <c r="F6" s="57">
         <v>365</v>
       </c>
-      <c r="G6" s="58">
+      <c r="G6" s="57">
         <v>365</v>
       </c>
-      <c r="H6" s="58">
+      <c r="H6" s="57">
         <v>365</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -9839,24 +9850,24 @@
       <c r="N6" s="7"/>
     </row>
     <row r="7" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D7" s="41" t="str">
+      <c r="D7" s="1" t="str">
         <f>"Average number of head between " &amp; TEXT(X_Cell_Site_StartDate, "dd mmm yy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "dd mmm yy")</f>
         <v>Average number of head between 01 Jan 24 and 31 Dec 24</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="57">
         <v>100</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="57">
         <v>100</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="57">
         <v>100</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="57">
         <v>100</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J7" s="3"/>
       <c r="N7" s="7"/>
@@ -9873,64 +9884,64 @@
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>173</v>
-      </c>
       <c r="N9" s="7"/>
     </row>
     <row r="10" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="118" t="str">
+      <c r="A10" s="117" t="str">
         <f>HYPERLINK("#'Input - Swine'!A1", "Swine")</f>
         <v>Swine</v>
       </c>
+      <c r="D10" s="6" t="s">
+        <v>225</v>
+      </c>
       <c r="N10" s="7"/>
     </row>
     <row r="11" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="56" t="s">
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D12" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="97" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="97" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" s="97" t="s">
         <v>125</v>
-      </c>
-      <c r="E11" s="98" t="s">
-        <v>105</v>
-      </c>
-      <c r="F11" s="98" t="s">
-        <v>106</v>
-      </c>
-      <c r="G11" s="98" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="98" t="s">
-        <v>127</v>
-      </c>
-      <c r="N11" s="7"/>
-    </row>
-    <row r="12" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="45" cm="1">
-        <f t="array" ref="E12">Common_InputFunctions.Utility_LookupValueInTableNumber(E11, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
-        <v>2.62</v>
-      </c>
-      <c r="F12" s="45" cm="1">
-        <f t="array" ref="F12">Common_InputFunctions.Utility_LookupValueInTableNumber(F11, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G12" s="45" cm="1">
-        <f t="array" ref="G12">Common_InputFunctions.Utility_LookupValueInTableNumber(G11, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
-        <v>2.5</v>
-      </c>
-      <c r="H12" s="45" cm="1">
-        <f t="array" ref="H12">Common_InputFunctions.Utility_LookupValueInTableNumber(H11, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
-        <v>1.71</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="N12" s="7"/>
     </row>
     <row r="13" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>54</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E13" s="44" cm="1">
+        <f t="array" ref="E13">Common_InputFunctions.Utility_LookupValueInTableNumber(E12, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
+        <v>2.62</v>
+      </c>
+      <c r="F13" s="44" cm="1">
+        <f t="array" ref="F13">Common_InputFunctions.Utility_LookupValueInTableNumber(F12, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G13" s="44" cm="1">
+        <f t="array" ref="G13">Common_InputFunctions.Utility_LookupValueInTableNumber(G12, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
+        <v>2.5</v>
+      </c>
+      <c r="H13" s="44" cm="1">
+        <f t="array" ref="H13">Common_InputFunctions.Utility_LookupValueInTableNumber(H12, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
+        <v>1.71</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="N13" s="34"/>
     </row>
@@ -9939,53 +9950,53 @@
         <f>HYPERLINK("#'3.5.1.1-2 Enteric Methane'!A1", "3.5.1.1-2 Enteric Methane")</f>
         <v>3.5.1.1-2 Enteric Methane</v>
       </c>
-      <c r="D14" s="56" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14" s="98" t="s">
+      <c r="N14" s="34"/>
+    </row>
+    <row r="15" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="97" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="97" t="s">
         <v>105</v>
       </c>
-      <c r="F14" s="98" t="s">
+      <c r="G15" s="97" t="s">
         <v>106</v>
       </c>
-      <c r="G14" s="98" t="s">
-        <v>107</v>
-      </c>
-      <c r="H14" s="98" t="s">
-        <v>127</v>
-      </c>
-      <c r="N14" s="34"/>
-    </row>
-    <row r="15" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="58" cm="1">
-        <f t="array" ref="E15">Common_InputFunctions.Utility_LookupValueInTableNumber(E14, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
+      <c r="H15" s="97" t="s">
+        <v>125</v>
+      </c>
+      <c r="N15" s="34"/>
+    </row>
+    <row r="16" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D16" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" s="57" cm="1">
+        <f t="array" ref="E16">Common_InputFunctions.Utility_LookupValueInTableNumber(E15, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
         <v>2.62</v>
       </c>
-      <c r="F15" s="58" cm="1">
-        <f t="array" ref="F15">Common_InputFunctions.Utility_LookupValueInTableNumber(F14, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
+      <c r="F16" s="57" cm="1">
+        <f t="array" ref="F16">Common_InputFunctions.Utility_LookupValueInTableNumber(F15, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="G15" s="58" cm="1">
-        <f t="array" ref="G15">Common_InputFunctions.Utility_LookupValueInTableNumber(G14, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
+      <c r="G16" s="57" cm="1">
+        <f t="array" ref="G16">Common_InputFunctions.Utility_LookupValueInTableNumber(G15, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
         <v>2.5</v>
       </c>
-      <c r="H15" s="58" cm="1">
-        <f t="array" ref="H15">Common_InputFunctions.Utility_LookupValueInTableNumber(H14, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
+      <c r="H16" s="57" cm="1">
+        <f t="array" ref="H16">Common_InputFunctions.Utility_LookupValueInTableNumber(H15, Table_SourceData_Swine_FeedIntake[Class],Table_SourceData_Swine_FeedIntake[Ij])</f>
         <v>1.71</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="N15" s="34"/>
-    </row>
-    <row r="16" spans="1:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I16" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="N16" s="34"/>
     </row>
     <row r="17" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="120" t="s">
         <v>1</v>
       </c>
       <c r="N17" s="7"/>
@@ -10006,8 +10017,8 @@
     </row>
     <row r="20" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
-        <v>Constants - Livestock</v>
+        <f>HYPERLINK("#'Constants - Common livestock'!A1", "Constants - Common livestock")</f>
+        <v>Constants - Common livestock</v>
       </c>
       <c r="N20" s="7"/>
     </row>
@@ -10377,7 +10388,7 @@
     <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="356" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D356" s="90"/>
+      <c r="D356" s="89"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E205:G205">
@@ -10530,11 +10541,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="e" vm="1">
+      <c r="A1" s="58" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:18" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10547,7 +10558,7 @@
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
@@ -10557,7 +10568,7 @@
       <c r="J3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
@@ -10600,7 +10611,7 @@
       <c r="A8" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="48"/>
+      <c r="D8" s="47"/>
     </row>
     <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
@@ -10613,7 +10624,7 @@
         <f>HYPERLINK("#'Input - Swine'!A1", "Swine")</f>
         <v>Swine</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="45" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="1" t="str" cm="1">
@@ -10622,10 +10633,10 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="46" t="s">
+      <c r="D11" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="47" t="str" cm="1">
+      <c r="E11" s="46" t="str" cm="1">
         <f t="array" ref="E11">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction_Unit()</f>
         <v>kg CH4/head/day</v>
       </c>
@@ -10635,89 +10646,89 @@
       <c r="A13" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="110" t="str" cm="1">
+      <c r="D13" s="109" t="str" cm="1">
         <f t="array" ref="D13:E16">_xlfn.CHOOSECOLS(EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction_Arguments(),1,2)</f>
         <v>I_j</v>
       </c>
-      <c r="E13" s="112" t="str">
+      <c r="E13" s="111" t="str">
         <v>daily feed ingested by each swine class</v>
       </c>
-      <c r="F13" s="111"/>
-      <c r="G13" s="110" t="str" cm="1">
+      <c r="F13" s="110"/>
+      <c r="G13" s="109" t="str" cm="1">
         <f t="array" ref="G13:H16">_xlfn.CHOOSECOLS(EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction_Arguments(),3,4)</f>
         <v>kg/head/day</v>
       </c>
-      <c r="H13" s="108" t="str">
+      <c r="H13" s="107" t="str">
         <v>Input</v>
       </c>
-      <c r="I13" s="110" t="str" cm="1">
+      <c r="I13" s="109" t="str" cm="1">
         <f t="array" aca="1" ref="I13" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$18), $D$18)</f>
         <v>M1_Table_I_j</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="119" t="str">
+      <c r="A14" s="118" t="str">
         <f>HYPERLINK("#'3.5.1.1-2 Enteric Methane'!A1", "3.5.1.1-2 Enteric Methane")</f>
         <v>3.5.1.1-2 Enteric Methane</v>
       </c>
-      <c r="D14" s="110" t="str">
+      <c r="D14" s="109" t="str">
         <v>18.6</v>
       </c>
-      <c r="E14" s="112" t="str">
+      <c r="E14" s="111" t="str">
         <v>gross energy (GE) content of feed</v>
       </c>
-      <c r="F14" s="111"/>
-      <c r="G14" s="110" t="str">
+      <c r="F14" s="110"/>
+      <c r="G14" s="109" t="str">
         <v>MJ GE/kg feed</v>
       </c>
-      <c r="H14" s="106" t="str">
+      <c r="H14" s="105" t="str">
         <v>Constant</v>
       </c>
-      <c r="I14" s="110" t="str">
+      <c r="I14" s="109" t="str">
         <f>D14</f>
         <v>18.6</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="110" t="str">
+      <c r="D15" s="109" t="str">
         <v>0.007</v>
       </c>
-      <c r="E15" s="112" t="str">
+      <c r="E15" s="111" t="str">
         <v>fraction of GE intake converted to methane by swine</v>
       </c>
-      <c r="F15" s="111"/>
-      <c r="G15" s="110" t="str">
+      <c r="F15" s="110"/>
+      <c r="G15" s="109" t="str">
         <v>fraction</v>
       </c>
-      <c r="H15" s="106" t="str">
+      <c r="H15" s="105" t="str">
         <v>Constant</v>
       </c>
-      <c r="I15" s="110" t="str">
+      <c r="I15" s="109" t="str">
         <f>D15</f>
         <v>0.007</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="110" t="str">
+      <c r="D16" s="109" t="str">
         <v>F</v>
       </c>
-      <c r="E16" s="112" t="str">
+      <c r="E16" s="111" t="str">
         <v>megajoules per kilogram of methane</v>
       </c>
-      <c r="F16" s="111"/>
-      <c r="G16" s="110" t="str">
+      <c r="F16" s="110"/>
+      <c r="G16" s="109" t="str">
         <v>MJ/kg CH4</v>
       </c>
-      <c r="H16" s="106" t="str">
+      <c r="H16" s="105" t="str">
         <v>Constant</v>
       </c>
-      <c r="I16" s="110">
+      <c r="I16" s="109">
         <f>SourceData_Swine_MegajoulesPerKilogramMethane_Data</f>
         <v>55.22</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="120" t="s">
         <v>1</v>
       </c>
     </row>
@@ -10726,11 +10737,11 @@
         <f>HYPERLINK("#'Constants - Swine'!A1", "Constants - Swine")</f>
         <v>Constants - Swine</v>
       </c>
-      <c r="D18" s="101" t="s">
-        <v>153</v>
-      </c>
-      <c r="M18" s="101" t="s">
-        <v>171</v>
+      <c r="D18" s="100" t="s">
+        <v>151</v>
+      </c>
+      <c r="M18" s="100" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10738,47 +10749,47 @@
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
-      <c r="D19" s="102" t="s">
-        <v>154</v>
-      </c>
-      <c r="M19" s="102" t="s">
-        <v>172</v>
+      <c r="D19" s="101" t="s">
+        <v>152</v>
+      </c>
+      <c r="M19" s="101" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
-        <v>Constants - Livestock</v>
-      </c>
-      <c r="D20" s="99" t="str" cm="1">
-        <f t="array" aca="1" ref="D20:G21" ca="1">OFFSET(X_Table_Swine_VolatileSolidProduction_Method1,0,1,2,4)</f>
+        <f>HYPERLINK("#'Constants - Common livestock'!A1", "Constants - Common livestock")</f>
+        <v>Constants - Common livestock</v>
+      </c>
+      <c r="D20" s="98" t="str" cm="1">
+        <f t="array" aca="1" ref="D20:G21" ca="1">OFFSET(X_Table_Swine_FeedIntake_Method1,0,1,2,4)</f>
         <v>Boars</v>
       </c>
-      <c r="E20" s="99" t="str">
+      <c r="E20" s="98" t="str">
         <f ca="1"/>
         <v>Sows</v>
       </c>
-      <c r="F20" s="99" t="str">
+      <c r="F20" s="98" t="str">
         <f ca="1"/>
         <v>Gilts</v>
       </c>
-      <c r="G20" s="99" t="str">
+      <c r="G20" s="98" t="str">
         <f ca="1"/>
         <v>Others</v>
       </c>
-      <c r="M20" s="99" t="str" cm="1">
-        <f t="array" aca="1" ref="M20:P21" ca="1">OFFSET(X_Table_Swine_VolatileSolidProduction_Method2,0,1,2,4)</f>
+      <c r="M20" s="98" t="str" cm="1">
+        <f t="array" aca="1" ref="M20:P21" ca="1">OFFSET(X_Table_Swine_FeedIntake_Method2,0,1,2,4)</f>
         <v>Boars</v>
       </c>
-      <c r="N20" s="99" t="str">
+      <c r="N20" s="98" t="str">
         <f ca="1"/>
         <v>Sows</v>
       </c>
-      <c r="O20" s="99" t="str">
+      <c r="O20" s="98" t="str">
         <f ca="1"/>
         <v>Gilts</v>
       </c>
-      <c r="P20" s="99" t="str">
+      <c r="P20" s="98" t="str">
         <f ca="1"/>
         <v>Others</v>
       </c>
@@ -10788,19 +10799,19 @@
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
       </c>
-      <c r="D21" s="50">
+      <c r="D21" s="49">
         <f ca="1"/>
         <v>2.62</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="49">
         <f ca="1"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="F21" s="50">
+      <c r="F21" s="49">
         <f ca="1"/>
         <v>2.5</v>
       </c>
-      <c r="G21" s="50">
+      <c r="G21" s="49">
         <f ca="1"/>
         <v>1.71</v>
       </c>
@@ -10808,19 +10819,19 @@
         <f>G13</f>
         <v>kg/head/day</v>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="49">
         <f ca="1"/>
         <v>2.62</v>
       </c>
-      <c r="N21" s="50">
+      <c r="N21" s="49">
         <f ca="1"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="O21" s="50">
+      <c r="O21" s="49">
         <f ca="1"/>
         <v>2.5</v>
       </c>
-      <c r="P21" s="50">
+      <c r="P21" s="49">
         <f ca="1"/>
         <v>1.71</v>
       </c>
@@ -10831,61 +10842,61 @@
     </row>
     <row r="22" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="101" t="s">
-        <v>155</v>
-      </c>
-      <c r="M23" s="101" t="s">
-        <v>155</v>
+      <c r="D23" s="100" t="s">
+        <v>153</v>
+      </c>
+      <c r="M23" s="100" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="102" t="s">
-        <v>156</v>
-      </c>
-      <c r="M24" s="102" t="s">
-        <v>156</v>
+      <c r="D24" s="101" t="s">
+        <v>154</v>
+      </c>
+      <c r="M24" s="101" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="F25" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="F25" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G25" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="M25" s="44" t="s">
+      <c r="G25" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="M25" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="N25" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="N25" s="44" t="s">
+      <c r="O25" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="O25" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="P25" s="44" t="s">
-        <v>127</v>
+      <c r="P25" s="43" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="50" cm="1">
+      <c r="D26" s="49" cm="1">
         <f t="array" aca="1" ref="D26" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction(D21,$I$16)</f>
         <v>6.1775443679826158E-3</v>
       </c>
-      <c r="E26" s="50" cm="1">
+      <c r="E26" s="49" cm="1">
         <f t="array" aca="1" ref="E26" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction(E21,$I$16)</f>
         <v>5.4230351321984793E-3</v>
       </c>
-      <c r="F26" s="50" cm="1">
+      <c r="F26" s="49" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction(F21,$I$16)</f>
         <v>5.8946034045635641E-3</v>
       </c>
-      <c r="G26" s="50" cm="1">
+      <c r="G26" s="49" cm="1">
         <f t="array" aca="1" ref="G26" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction(G21,$I$16)</f>
         <v>4.031908728721478E-3</v>
       </c>
@@ -10893,19 +10904,19 @@
         <f>$E$11</f>
         <v>kg CH4/head/day</v>
       </c>
-      <c r="M26" s="50" cm="1">
+      <c r="M26" s="49" cm="1">
         <f t="array" aca="1" ref="M26" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction(M21,$I$16)</f>
         <v>6.1775443679826158E-3</v>
       </c>
-      <c r="N26" s="50" cm="1">
+      <c r="N26" s="49" cm="1">
         <f t="array" aca="1" ref="N26" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction(N21,$I$16)</f>
         <v>5.4230351321984793E-3</v>
       </c>
-      <c r="O26" s="50" cm="1">
+      <c r="O26" s="49" cm="1">
         <f t="array" aca="1" ref="O26" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction(O21,$I$16)</f>
         <v>5.8946034045635641E-3</v>
       </c>
-      <c r="P26" s="50" cm="1">
+      <c r="P26" s="49" cm="1">
         <f t="array" aca="1" ref="P26" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__2_DailyEntericMethaneProduction(P21,$I$16)</f>
         <v>4.031908728721478E-3</v>
       </c>
@@ -10953,7 +10964,7 @@
     </row>
     <row r="35" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D36" s="46" t="s">
+      <c r="D36" s="45" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="1" t="str" cm="1">
@@ -10962,117 +10973,117 @@
       </c>
     </row>
     <row r="37" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D37" s="46" t="s">
+      <c r="D37" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="E37" s="47" t="str" cm="1">
+      <c r="E37" s="46" t="str" cm="1">
         <f t="array" ref="E37">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Unit()</f>
         <v>t CH4</v>
       </c>
     </row>
     <row r="38" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="50" t="str" cm="1">
+      <c r="D39" s="49" t="str" cm="1">
         <f t="array" ref="D39:E41">_xlfn.CHOOSECOLS(EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Arguments(), 1, 2)</f>
         <v>N_j</v>
       </c>
-      <c r="E39" s="51" t="str">
+      <c r="E39" s="50" t="str">
         <v>numbers of swine of each class</v>
       </c>
-      <c r="F39" s="52"/>
-      <c r="G39" s="50" t="str" cm="1">
+      <c r="F39" s="51"/>
+      <c r="G39" s="49" t="str" cm="1">
         <f t="array" ref="G39:H41">_xlfn.CHOOSECOLS(EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Arguments(), 3,4)</f>
         <v>head</v>
       </c>
-      <c r="H39" s="107" t="str">
+      <c r="H39" s="106" t="str">
         <v>Input</v>
       </c>
-      <c r="I39" s="109" t="str" cm="1">
+      <c r="I39" s="108" t="str" cm="1">
         <f t="array" aca="1" ref="I39" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$48), $D$48)</f>
         <v>Table_N_j</v>
       </c>
     </row>
     <row r="40" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="50" t="str">
+      <c r="D40" s="49" t="str">
         <v>M_j</v>
       </c>
-      <c r="E40" s="51" t="str">
+      <c r="E40" s="50" t="str">
         <v>methane production</v>
       </c>
-      <c r="F40" s="52"/>
-      <c r="G40" s="50" t="str">
+      <c r="F40" s="51"/>
+      <c r="G40" s="49" t="str">
         <v>kg CH4/head/day</v>
       </c>
-      <c r="H40" s="106" t="str">
+      <c r="H40" s="105" t="str">
         <v>Calculated from 3.5.1.1, (2)</v>
       </c>
-      <c r="I40" s="109" t="str" cm="1">
+      <c r="I40" s="108" t="str" cm="1">
         <f t="array" aca="1" ref="I40" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$23), $D$23)</f>
         <v>M1_Table_M_j</v>
       </c>
     </row>
     <row r="41" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D41" s="50" t="str">
+      <c r="D41" s="49" t="str">
         <v>D_j</v>
       </c>
-      <c r="E41" s="51" t="str">
+      <c r="E41" s="50" t="str">
         <v>the average number of days on farm for each swine class</v>
       </c>
-      <c r="F41" s="52"/>
-      <c r="G41" s="50" t="str">
+      <c r="F41" s="51"/>
+      <c r="G41" s="49" t="str">
         <v>days</v>
       </c>
-      <c r="H41" s="107" t="str">
+      <c r="H41" s="106" t="str">
         <v>Input</v>
       </c>
-      <c r="I41" s="109" t="str" cm="1">
+      <c r="I41" s="108" t="str" cm="1">
         <f t="array" aca="1" ref="I41" ca="1">HYPERLINK(Common_InputFunctions.Utility_SourceHyperlink($D$43), $D$43)</f>
         <v>Table_D_j</v>
       </c>
     </row>
     <row r="42" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="43" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="101" t="s">
-        <v>120</v>
+      <c r="D43" s="100" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D44" s="102" t="s">
-        <v>121</v>
+      <c r="D44" s="101" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D45" s="99" t="str" cm="1">
+      <c r="D45" s="98" t="str" cm="1">
         <f t="array" aca="1" ref="D45:G46" ca="1">OFFSET(X_Table_Swine_HerdMovement,0,1,2,4)</f>
         <v>Boars</v>
       </c>
-      <c r="E45" s="99" t="str">
+      <c r="E45" s="98" t="str">
         <f ca="1"/>
         <v>Sows</v>
       </c>
-      <c r="F45" s="99" t="str">
+      <c r="F45" s="98" t="str">
         <f ca="1"/>
         <v>Gilts</v>
       </c>
-      <c r="G45" s="99" t="str">
+      <c r="G45" s="98" t="str">
         <f ca="1"/>
         <v>Others</v>
       </c>
     </row>
     <row r="46" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D46" s="103">
+      <c r="D46" s="102">
         <f ca="1"/>
         <v>365</v>
       </c>
-      <c r="E46" s="103">
+      <c r="E46" s="102">
         <f ca="1"/>
         <v>365</v>
       </c>
-      <c r="F46" s="103">
+      <c r="F46" s="102">
         <f ca="1"/>
         <v>365</v>
       </c>
-      <c r="G46" s="103">
+      <c r="G46" s="102">
         <f ca="1"/>
         <v>365</v>
       </c>
@@ -11083,43 +11094,43 @@
     </row>
     <row r="47" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D48" s="101" t="s">
-        <v>122</v>
+      <c r="D48" s="100" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D49" s="102" t="s">
-        <v>123</v>
+      <c r="D49" s="101" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D50" s="99" t="s">
+      <c r="D50" s="98" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" s="98" t="s">
         <v>105</v>
       </c>
-      <c r="E50" s="99" t="s">
+      <c r="F50" s="98" t="s">
         <v>106</v>
       </c>
-      <c r="F50" s="99" t="s">
-        <v>107</v>
-      </c>
-      <c r="G50" s="99" t="s">
-        <v>127</v>
+      <c r="G50" s="98" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D51" s="103" cm="1">
+      <c r="D51" s="102" cm="1">
         <f t="array" aca="1" ref="D51:G51" ca="1">OFFSET(X_Table_Swine_HerdMovement,2,1,1,4)</f>
         <v>100</v>
       </c>
-      <c r="E51" s="103">
+      <c r="E51" s="102">
         <f ca="1"/>
         <v>100</v>
       </c>
-      <c r="F51" s="103">
+      <c r="F51" s="102">
         <f ca="1"/>
         <v>100</v>
       </c>
-      <c r="G51" s="103">
+      <c r="G51" s="102">
         <f ca="1"/>
         <v>100</v>
       </c>
@@ -11130,61 +11141,61 @@
     </row>
     <row r="52" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="101" t="s">
-        <v>158</v>
-      </c>
-      <c r="M53" s="101" t="s">
-        <v>161</v>
+      <c r="D53" s="100" t="s">
+        <v>156</v>
+      </c>
+      <c r="M53" s="100" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="102" t="s">
-        <v>159</v>
-      </c>
-      <c r="M54" s="102" t="s">
-        <v>162</v>
+      <c r="D54" s="101" t="s">
+        <v>157</v>
+      </c>
+      <c r="M54" s="101" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D55" s="44" t="s">
+      <c r="D55" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="E55" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="E55" s="44" t="s">
+      <c r="F55" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="F55" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="G55" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="M55" s="44" t="s">
+      <c r="G55" s="43" t="s">
+        <v>125</v>
+      </c>
+      <c r="M55" s="43" t="s">
+        <v>104</v>
+      </c>
+      <c r="N55" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="N55" s="44" t="s">
+      <c r="O55" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="O55" s="44" t="s">
-        <v>107</v>
-      </c>
-      <c r="P55" s="44" t="s">
-        <v>127</v>
+      <c r="P55" s="43" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D56" s="45" cm="1">
+      <c r="D56" s="44" cm="1">
         <f t="array" aca="1" ref="D56" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation($D51,D26,$D46)</f>
         <v>0.22548036943136548</v>
       </c>
-      <c r="E56" s="45" cm="1">
+      <c r="E56" s="44" cm="1">
         <f t="array" aca="1" ref="E56" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation($E51,E26,$E46)</f>
         <v>0.19794078232524451</v>
       </c>
-      <c r="F56" s="45" cm="1">
+      <c r="F56" s="44" cm="1">
         <f t="array" aca="1" ref="F56" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation($F51,F26,$F46)</f>
         <v>0.2151530242665701</v>
       </c>
-      <c r="G56" s="45" cm="1">
+      <c r="G56" s="44" cm="1">
         <f t="array" aca="1" ref="G56" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation($G51,G26,$G46)</f>
         <v>0.14716466859833394</v>
       </c>
@@ -11192,19 +11203,19 @@
         <f>$E$37</f>
         <v>t CH4</v>
       </c>
-      <c r="M56" s="45" cm="1">
+      <c r="M56" s="44" cm="1">
         <f t="array" aca="1" ref="M56" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation($D51,M26,$D46)</f>
         <v>0.22548036943136548</v>
       </c>
-      <c r="N56" s="45" cm="1">
+      <c r="N56" s="44" cm="1">
         <f t="array" aca="1" ref="N56" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation($E51,N26,$E46)</f>
         <v>0.19794078232524451</v>
       </c>
-      <c r="O56" s="45" cm="1">
+      <c r="O56" s="44" cm="1">
         <f t="array" aca="1" ref="O56" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation($F51,O26,$F46)</f>
         <v>0.2151530242665701</v>
       </c>
-      <c r="P56" s="45" cm="1">
+      <c r="P56" s="44" cm="1">
         <f t="array" aca="1" ref="P56" ca="1">EntericMethane_Swine_Equations.VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation($G51,P26,$G46)</f>
         <v>0.14716466859833394</v>
       </c>
@@ -11215,101 +11226,101 @@
     </row>
     <row r="57" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D58" s="85" t="s">
-        <v>124</v>
-      </c>
-      <c r="E58" s="86">
+      <c r="D58" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="E58" s="85">
         <f ca="1">SUM(D56:G56)</f>
         <v>0.78573884462151411</v>
       </c>
-      <c r="F58" s="87" t="str">
+      <c r="F58" s="86" t="str">
         <f>$E$37</f>
         <v>t CH4</v>
       </c>
-      <c r="M58" s="85" t="s">
-        <v>124</v>
-      </c>
-      <c r="N58" s="86">
+      <c r="M58" s="84" t="s">
+        <v>122</v>
+      </c>
+      <c r="N58" s="85">
         <f ca="1">SUM(M56:P56)</f>
         <v>0.78573884462151411</v>
       </c>
-      <c r="O58" s="87" t="str">
+      <c r="O58" s="86" t="str">
         <f>$E$37</f>
         <v>t CH4</v>
       </c>
     </row>
     <row r="59" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D60" s="50" t="str" cm="1">
+      <c r="D60" s="49" t="str" cm="1">
         <f t="array" ref="D60:E61">Common_Equations.Common_ConvertCH4ToCO2e_Arguments()</f>
         <v>ECH4</v>
       </c>
-      <c r="E60" s="51" t="str">
+      <c r="E60" s="50" t="str">
         <v>Methane emissions (t CH4)</v>
       </c>
-      <c r="F60" s="88"/>
-      <c r="G60" s="45">
+      <c r="F60" s="87"/>
+      <c r="G60" s="44">
         <f ca="1">VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method1</f>
         <v>0.78573884462151411</v>
       </c>
-      <c r="M60" s="50" t="str" cm="1">
+      <c r="M60" s="49" t="str" cm="1">
         <f t="array" ref="M60:N61">Common_Equations.Common_ConvertCH4ToCO2e_Arguments()</f>
         <v>ECH4</v>
       </c>
-      <c r="N60" s="51" t="str">
+      <c r="N60" s="50" t="str">
         <v>Methane emissions (t CH4)</v>
       </c>
-      <c r="O60" s="88"/>
-      <c r="P60" s="45">
+      <c r="O60" s="87"/>
+      <c r="P60" s="44">
         <f ca="1">VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method2</f>
         <v>0.78573884462151411</v>
       </c>
     </row>
     <row r="61" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D61" s="50" t="str">
+      <c r="D61" s="49" t="str">
         <v>GWPCH4</v>
       </c>
-      <c r="E61" s="51" t="str">
+      <c r="E61" s="50" t="str">
         <v>Global warming potential for methane (t CO2-e / t CH4)</v>
       </c>
-      <c r="F61" s="88"/>
-      <c r="G61" s="45">
+      <c r="F61" s="87"/>
+      <c r="G61" s="44">
         <f>Common_InputFunctions.Utility_LookupValueInTableNumber("CH4",Table_GWPData[Gas],Table_GWPData[CO2-e factor])</f>
         <v>28</v>
       </c>
-      <c r="M61" s="50" t="str">
+      <c r="M61" s="49" t="str">
         <v>GWPCH4</v>
       </c>
-      <c r="N61" s="51" t="str">
+      <c r="N61" s="50" t="str">
         <v>Global warming potential for methane (t CO2-e / t CH4)</v>
       </c>
-      <c r="O61" s="88"/>
-      <c r="P61" s="45">
+      <c r="O61" s="87"/>
+      <c r="P61" s="44">
         <f>Common_InputFunctions.Utility_LookupValueInTableNumber("CH4",Table_GWPData[Gas],Table_GWPData[CO2-e factor])</f>
         <v>28</v>
       </c>
     </row>
     <row r="62" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="4:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D63" s="94" t="s">
-        <v>160</v>
+      <c r="D63" s="93" t="s">
+        <v>158</v>
       </c>
       <c r="E63" s="39" cm="1">
         <f t="array" aca="1" ref="E63" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(G60,G61)</f>
         <v>22.000687649402394</v>
       </c>
-      <c r="F63" s="89" t="str" cm="1">
+      <c r="F63" s="88" t="str" cm="1">
         <f t="array" ref="F63">Common_Equations.Common_ConvertN2OToCO2e_Unit()</f>
         <v>t CO2e</v>
       </c>
-      <c r="M63" s="94" t="s">
-        <v>160</v>
+      <c r="M63" s="93" t="s">
+        <v>158</v>
       </c>
       <c r="N63" s="39" cm="1">
         <f t="array" aca="1" ref="N63" ca="1">Common_Equations.Common_ConvertCH4ToCO2e(P60,P61)</f>
         <v>22.000687649402394</v>
       </c>
-      <c r="O63" s="89" t="str" cm="1">
+      <c r="O63" s="88" t="str" cm="1">
         <f t="array" ref="O63">Common_Equations.Common_ConvertN2OToCO2e_Unit()</f>
         <v>t CO2e</v>
       </c>
@@ -11437,7 +11448,7 @@
     <row r="184" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="185" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="186" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="113" t="str">
+      <c r="A186" s="112" t="str">
         <f>HYPERLINK("#A1", "▲ Back to top")</f>
         <v>▲ Back to top</v>
       </c>
@@ -11469,7 +11480,7 @@
     <row r="211" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="212" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="213" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="113" t="str">
+      <c r="A213" s="112" t="str">
         <f>HYPERLINK("#A1", "▲ Back to top")</f>
         <v>▲ Back to top</v>
       </c>
@@ -11492,7 +11503,7 @@
     <row r="229" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="230" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="231" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="113" t="str">
+      <c r="A231" s="112" t="str">
         <f>HYPERLINK("#A1", "▲ Back to top")</f>
         <v>▲ Back to top</v>
       </c>
@@ -11532,7 +11543,7 @@
     <row r="264" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="265" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="266" spans="1:1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="113" t="str">
+      <c r="A266" s="112" t="str">
         <f>HYPERLINK("#A1", "▲ Back to top")</f>
         <v>▲ Back to top</v>
       </c>
@@ -11579,11 +11590,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="8" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="e" vm="1">
+      <c r="A1" s="58" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:21" s="9" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11630,14 +11641,20 @@
     </row>
     <row r="6" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11645,10 +11662,13 @@
         <v>0</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>223</v>
       </c>
       <c r="M8" s="1"/>
     </row>
@@ -11658,10 +11678,13 @@
         <v>Site</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>104</v>
       </c>
       <c r="M9" s="1"/>
     </row>
@@ -11671,22 +11694,31 @@
         <v>Swine</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>105</v>
       </c>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>106</v>
       </c>
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>125</v>
       </c>
       <c r="M12" s="1"/>
     </row>
@@ -11695,7 +11727,7 @@
         <v>54</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M13" s="1"/>
     </row>
@@ -11718,17 +11750,17 @@
       <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D16" s="48" t="str" cm="1">
+      <c r="D16" s="47" t="str" cm="1">
         <f t="array" ref="D16">SourceData_Swine.SourceData_Swine_FracLEACH_DrylotMMS_Variation()</f>
         <v>VARIATION ON SOURCE: Text refers to 'solid storage' MMS, but equation refers to 'drylot' MMS.</v>
       </c>
       <c r="M16" s="1"/>
     </row>
     <row r="17" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="46" t="str" cm="1">
+      <c r="D17" s="45" t="str" cm="1">
         <f t="array" ref="D17">SourceData_Swine.SourceData_Swine_FracLEACH_DrylotMMS_Variable()</f>
         <v>FracLEACH_MS</v>
       </c>
@@ -11736,14 +11768,14 @@
         <f t="array" ref="E17">SourceData_Swine.SourceData_Swine_FracLEACH_DrylotMMS_Data()</f>
         <v>0.02</v>
       </c>
-      <c r="F17" s="47" t="str" cm="1">
+      <c r="F17" s="46" t="str" cm="1">
         <f t="array" ref="F17">SourceData_Swine.SourceData_Swine_FracLEACH_DrylotMMS_Unit()</f>
         <v>fraction</v>
       </c>
       <c r="M17" s="1"/>
     </row>
     <row r="18" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="120" t="str">
+      <c r="A18" s="119" t="str">
         <f>HYPERLINK("#'Constants - Swine'!A1", "Constants - Swine")</f>
         <v>Constants - Swine</v>
       </c>
@@ -11762,8 +11794,8 @@
     </row>
     <row r="20" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
-        <v>Constants - Livestock</v>
+        <f>HYPERLINK("#'Constants - Common livestock'!A1", "Constants - Common livestock")</f>
+        <v>Constants - Common livestock</v>
       </c>
       <c r="D20" s="5" t="str" cm="1">
         <f t="array" ref="D20">SourceData_Swine.SourceData_Swine_MethaneVolatileSolidsEmissionsPotential_Source()</f>
@@ -11776,7 +11808,7 @@
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
       </c>
-      <c r="D21" s="46" t="str" cm="1">
+      <c r="D21" s="45" t="str" cm="1">
         <f t="array" ref="D21">SourceData_Swine.SourceData_Swine_MethaneVolatileSolidsEmissionsPotential_Variable()</f>
         <v>B0</v>
       </c>
@@ -11784,7 +11816,7 @@
         <f t="array" ref="E21">SourceData_Swine.SourceData_Swine_MethaneVolatileSolidsEmissionsPotential_Data()</f>
         <v>0.19</v>
       </c>
-      <c r="F21" s="47" t="str" cm="1">
+      <c r="F21" s="46" t="str" cm="1">
         <f t="array" ref="F21">SourceData_Swine.SourceData_Swine_MethaneVolatileSolidsEmissionsPotential_Unit()</f>
         <v>m3 CH4 / kg VS</v>
       </c>
@@ -11801,8 +11833,8 @@
         <f t="array" ref="D24">SourceData_Swine.SourceData_Swine_MMS_MCFs_Title()</f>
         <v>Methane conversion factor for temperature zone and manure management system.</v>
       </c>
-      <c r="H24" s="91" t="s">
-        <v>111</v>
+      <c r="H24" s="90" t="s">
+        <v>109</v>
       </c>
       <c r="M24" s="1"/>
     </row>
@@ -11811,13 +11843,13 @@
         <f t="array" ref="D25">SourceData_Swine.SourceData_Swine_MMS_MCFs_Source()</f>
         <v>VEERG 2026: Table A.1.6.4: Swine - MCFs (MCFim)</v>
       </c>
-      <c r="H25" s="91" t="s">
-        <v>112</v>
+      <c r="H25" s="90" t="s">
+        <v>110</v>
       </c>
       <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="48" t="str" cm="1">
+      <c r="D26" s="47" t="str" cm="1">
         <f t="array" ref="D26">SourceData_Swine.SourceData_Swine_MMS_MCFs_Variation()</f>
         <v>VARIATION ON SOURCE DATA: Added columns for ACT, split QLD and NT. Added extra column with MMS names that match NIR definitions</v>
       </c>
@@ -11831,31 +11863,31 @@
         <v>48</v>
       </c>
       <c r="E28" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="F28" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28" s="33" t="s">
+      <c r="I28" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="I28" s="33" t="s">
+      <c r="J28" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="J28" s="33" t="s">
+      <c r="K28" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="K28" s="33" t="s">
+      <c r="L28" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="L28" s="33" t="s">
-        <v>66</v>
-      </c>
       <c r="M28" s="33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12160,13 +12192,13 @@
     </row>
     <row r="38" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K38" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="M38" s="1"/>
     </row>
@@ -12174,187 +12206,187 @@
       <c r="M39" s="1"/>
     </row>
     <row r="40" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="100" t="s">
+      <c r="D40" s="99" t="s">
         <v>48</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="G40" s="100" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" s="99" t="s">
         <v>48</v>
       </c>
       <c r="H40" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="K40" s="100" t="s">
+        <v>57</v>
+      </c>
+      <c r="K40" s="99" t="s">
         <v>48</v>
       </c>
       <c r="L40" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M40" s="1"/>
     </row>
     <row r="41" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="33" t="str">
-        <f>'Constants - Livestock'!$E$10</f>
+        <f>'Constants - Common livestock'!$E$10</f>
         <v>Anaerobic lagoon</v>
       </c>
       <c r="E41" s="33" t="str">
-        <f>'Constants - Livestock'!$F$10</f>
+        <f>'Constants - Common livestock'!$F$10</f>
         <v>Anaerobic lagoon (m=1)</v>
       </c>
       <c r="G41" s="33" t="str">
-        <f>'Constants - Livestock'!$E$10</f>
+        <f>'Constants - Common livestock'!$E$10</f>
         <v>Anaerobic lagoon</v>
       </c>
       <c r="H41" s="33" t="str">
-        <f>'Constants - Livestock'!$F$10</f>
+        <f>'Constants - Common livestock'!$F$10</f>
         <v>Anaerobic lagoon (m=1)</v>
       </c>
       <c r="K41" s="33" t="str">
-        <f>'Constants - Livestock'!$E$10</f>
+        <f>'Constants - Common livestock'!$E$10</f>
         <v>Anaerobic lagoon</v>
       </c>
       <c r="L41" s="33" t="str">
-        <f>'Constants - Livestock'!$F$10</f>
+        <f>'Constants - Common livestock'!$F$10</f>
         <v>Anaerobic lagoon (m=1)</v>
       </c>
       <c r="M41" s="1"/>
     </row>
     <row r="42" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="33" t="str">
-        <f>'Constants - Livestock'!$E$15</f>
+        <f>'Constants - Common livestock'!$E$15</f>
         <v>Solid storage</v>
       </c>
       <c r="E42" s="33" t="str">
-        <f>'Constants - Livestock'!$F$15</f>
+        <f>'Constants - Common livestock'!$F$15</f>
         <v>Solid storage (m=4)</v>
       </c>
       <c r="G42" s="33" t="str">
-        <f>'Constants - Livestock'!$E$16</f>
+        <f>'Constants - Common livestock'!$E$16</f>
         <v>Drylot (feed pad)</v>
       </c>
       <c r="H42" s="33" t="str">
-        <f>'Constants - Livestock'!$F$16</f>
+        <f>'Constants - Common livestock'!$F$16</f>
         <v>Drylot (feed pad) (m=5)</v>
       </c>
       <c r="K42" s="33" t="str">
-        <f>'Constants - Livestock'!$E$15</f>
+        <f>'Constants - Common livestock'!$E$15</f>
         <v>Solid storage</v>
       </c>
       <c r="L42" s="33" t="str">
-        <f>'Constants - Livestock'!$F$15</f>
+        <f>'Constants - Common livestock'!$F$15</f>
         <v>Solid storage (m=4)</v>
       </c>
       <c r="M42" s="1"/>
     </row>
     <row r="43" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="33" t="str">
-        <f>'Constants - Livestock'!$E$16</f>
+        <f>'Constants - Common livestock'!$E$16</f>
         <v>Drylot (feed pad)</v>
       </c>
       <c r="E43" s="33" t="str">
-        <f>'Constants - Livestock'!$F$16</f>
+        <f>'Constants - Common livestock'!$F$16</f>
         <v>Drylot (feed pad) (m=5)</v>
       </c>
       <c r="G43" s="33" t="str">
-        <f>'Constants - Livestock'!$E$18</f>
+        <f>'Constants - Common livestock'!$E$18</f>
         <v>Digester / covered lagoons</v>
       </c>
       <c r="H43" s="33" t="str">
-        <f>'Constants - Livestock'!$F$18</f>
+        <f>'Constants - Common livestock'!$F$18</f>
         <v>Digester / covered lagoons (m=7)</v>
       </c>
       <c r="K43" s="33" t="str">
-        <f>'Constants - Livestock'!$E$16</f>
+        <f>'Constants - Common livestock'!$E$16</f>
         <v>Drylot (feed pad)</v>
       </c>
       <c r="L43" s="33" t="str">
-        <f>'Constants - Livestock'!$F$16</f>
+        <f>'Constants - Common livestock'!$F$16</f>
         <v>Drylot (feed pad) (m=5)</v>
       </c>
       <c r="M43" s="1"/>
     </row>
     <row r="44" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="33" t="str">
-        <f>'Constants - Livestock'!$E$18</f>
+        <f>'Constants - Common livestock'!$E$18</f>
         <v>Digester / covered lagoons</v>
       </c>
       <c r="E44" s="33" t="str">
-        <f>'Constants - Livestock'!$F$18</f>
+        <f>'Constants - Common livestock'!$F$18</f>
         <v>Digester / covered lagoons (m=7)</v>
       </c>
       <c r="G44" s="33" t="str">
-        <f>'Constants - Livestock'!$E$19</f>
+        <f>'Constants - Common livestock'!$E$19</f>
         <v>Deep litter</v>
       </c>
       <c r="H44" s="33" t="str">
-        <f>'Constants - Livestock'!$F$19</f>
+        <f>'Constants - Common livestock'!$F$19</f>
         <v>Deep litter (m=8)</v>
       </c>
       <c r="K44" s="33" t="str">
-        <f>'Constants - Livestock'!$E$18</f>
+        <f>'Constants - Common livestock'!$E$18</f>
         <v>Digester / covered lagoons</v>
       </c>
       <c r="L44" s="33" t="str">
-        <f>'Constants - Livestock'!$F$18</f>
+        <f>'Constants - Common livestock'!$F$18</f>
         <v>Digester / covered lagoons (m=7)</v>
       </c>
       <c r="M44" s="1"/>
     </row>
     <row r="45" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="33" t="str">
-        <f>'Constants - Livestock'!$E$19</f>
+        <f>'Constants - Common livestock'!$E$19</f>
         <v>Deep litter</v>
       </c>
       <c r="E45" s="33" t="str">
-        <f>'Constants - Livestock'!$F$19</f>
+        <f>'Constants - Common livestock'!$F$19</f>
         <v>Deep litter (m=8)</v>
       </c>
       <c r="G45" s="33" t="str">
-        <f>'Constants - Livestock'!$E$20</f>
+        <f>'Constants - Common livestock'!$E$20</f>
         <v>Pit storage</v>
       </c>
       <c r="H45" s="33" t="str">
-        <f>'Constants - Livestock'!$F$20</f>
+        <f>'Constants - Common livestock'!$F$20</f>
         <v>Pit storage (m=9)</v>
       </c>
       <c r="K45" s="33" t="str">
-        <f>'Constants - Livestock'!$E$19</f>
+        <f>'Constants - Common livestock'!$E$19</f>
         <v>Deep litter</v>
       </c>
       <c r="L45" s="33" t="str">
-        <f>'Constants - Livestock'!$F$19</f>
+        <f>'Constants - Common livestock'!$F$19</f>
         <v>Deep litter (m=8)</v>
       </c>
       <c r="M45" s="1"/>
     </row>
     <row r="46" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="33" t="str">
-        <f>'Constants - Livestock'!$E$20</f>
+        <f>'Constants - Common livestock'!$E$20</f>
         <v>Pit storage</v>
       </c>
       <c r="E46" s="33" t="str">
-        <f>'Constants - Livestock'!$F$20</f>
+        <f>'Constants - Common livestock'!$F$20</f>
         <v>Pit storage (m=9)</v>
       </c>
       <c r="K46" s="33" t="str">
-        <f>'Constants - Livestock'!$E$20</f>
+        <f>'Constants - Common livestock'!$E$20</f>
         <v>Pit storage</v>
       </c>
       <c r="L46" s="33" t="str">
-        <f>'Constants - Livestock'!$F$20</f>
+        <f>'Constants - Common livestock'!$F$20</f>
         <v>Pit storage (m=9)</v>
       </c>
       <c r="M46" s="1"/>
     </row>
     <row r="47" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="33" t="str">
-        <f>'Constants - Livestock'!$E$26</f>
+        <f>'Constants - Common livestock'!$E$26</f>
         <v>Direct application</v>
       </c>
       <c r="E47" s="33" t="str">
-        <f>'Constants - Livestock'!$F$26</f>
+        <f>'Constants - Common livestock'!$F$26</f>
         <v>Direct application (m=13)</v>
       </c>
       <c r="M47" s="1"/>
@@ -12370,10 +12402,10 @@
     </row>
     <row r="51" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M51" s="1"/>
     </row>
@@ -12381,20 +12413,20 @@
       <c r="M52" s="1"/>
     </row>
     <row r="53" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D53" s="100" t="s">
+      <c r="D53" s="99" t="s">
         <v>48</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G53" s="33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M53" s="1"/>
     </row>
     <row r="54" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="33" t="str">
-        <f>'Constants - Livestock'!$E$10</f>
+        <f>'Constants - Common livestock'!$E$10</f>
         <v>Anaerobic lagoon</v>
       </c>
       <c r="E54" s="33">
@@ -12408,7 +12440,7 @@
     </row>
     <row r="55" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="33" t="str">
-        <f>'Constants - Livestock'!$E$15</f>
+        <f>'Constants - Common livestock'!$E$15</f>
         <v>Solid storage</v>
       </c>
       <c r="E55" s="33">
@@ -12422,7 +12454,7 @@
     </row>
     <row r="56" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="33" t="str">
-        <f>'Constants - Livestock'!$E$16</f>
+        <f>'Constants - Common livestock'!$E$16</f>
         <v>Drylot (feed pad)</v>
       </c>
       <c r="E56" s="33">
@@ -12436,7 +12468,7 @@
     </row>
     <row r="57" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="33" t="str">
-        <f>'Constants - Livestock'!$E$18</f>
+        <f>'Constants - Common livestock'!$E$18</f>
         <v>Digester / covered lagoons</v>
       </c>
       <c r="E57" s="33">
@@ -12446,7 +12478,7 @@
     </row>
     <row r="58" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="33" t="str">
-        <f>'Constants - Livestock'!$E$19</f>
+        <f>'Constants - Common livestock'!$E$19</f>
         <v>Deep litter</v>
       </c>
       <c r="E58" s="33">
@@ -12456,7 +12488,7 @@
     </row>
     <row r="59" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="33" t="str">
-        <f>'Constants - Livestock'!$E$20</f>
+        <f>'Constants - Common livestock'!$E$20</f>
         <v>Pit storage</v>
       </c>
       <c r="E59" s="33">
@@ -12466,7 +12498,7 @@
     </row>
     <row r="60" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="33" t="str">
-        <f>'Constants - Livestock'!$E$26</f>
+        <f>'Constants - Common livestock'!$E$26</f>
         <v>Direct application</v>
       </c>
       <c r="E60" s="33">
@@ -12495,7 +12527,7 @@
       <c r="M64" s="1"/>
     </row>
     <row r="65" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D65" s="48" t="str" cm="1">
+      <c r="D65" s="47" t="str" cm="1">
         <f t="array" ref="D65">SourceData_Swine.SourceData_Swine_VolatileSolids_Variation()</f>
         <v>VARIATION ON SOURCE DATA: Only uses data for 2020-2024. Use 'Slaughter pigs' data for 'Other j=4' class.</v>
       </c>
@@ -12506,10 +12538,10 @@
     </row>
     <row r="67" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E67" s="33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M67" s="1"/>
     </row>
@@ -12583,7 +12615,7 @@
       <c r="V75" s="1"/>
     </row>
     <row r="76" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D76" s="48" t="str" cm="1">
+      <c r="D76" s="47" t="str" cm="1">
         <f t="array" ref="D76">SourceData_Swine.SourceData_Swine_FeedIntake_Variation()</f>
         <v>VARIATION ON SOURCE DATA: Only uses data for 2020-2024. Use 'Slaughter pigs' data for 'Other j=4' class.</v>
       </c>
@@ -12596,10 +12628,10 @@
     </row>
     <row r="78" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E78" s="33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M78" s="1"/>
       <c r="V78" s="1"/>
@@ -12675,7 +12707,7 @@
       <c r="V86" s="1"/>
     </row>
     <row r="87" spans="4:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D87" s="48" t="str" cm="1">
+      <c r="D87" s="47" t="str" cm="1">
         <f t="array" ref="D87">SourceData_Swine.SourceData_Swine_NitrogenInWaste_Variation()</f>
         <v>VARIATION ON SOURCE DATA: Only uses data for 2020-2024. Use 'Slaughter pigs' data for 'Other j=4' class. Added 'NWj daily' column to provide daily value for Others class. Added 'Class name' column to aid lookup.</v>
       </c>
@@ -12688,16 +12720,16 @@
     </row>
     <row r="89" spans="4:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E89" s="33" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F89" s="33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G89" s="33" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M89" s="1"/>
       <c r="V89" s="1"/>
@@ -12805,7 +12837,7 @@
       <c r="M97" s="1"/>
     </row>
     <row r="98" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D98" s="48" t="str" cm="1">
+      <c r="D98" s="47" t="str" cm="1">
         <f t="array" ref="D98">SourceData_Swine.SourceData_Swine_FractionNVolatilised_Variation()</f>
         <v>VARIATION ON SOURCE DATA: Added 'NIR reference column to aid lookup.</v>
       </c>
@@ -12813,13 +12845,13 @@
     </row>
     <row r="99" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E99" s="33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F99" s="33" t="s">
         <v>131</v>
-      </c>
-      <c r="E99" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="F99" s="33" t="s">
-        <v>133</v>
       </c>
       <c r="M99" s="1"/>
     </row>
@@ -12934,7 +12966,7 @@
       <c r="M109" s="1"/>
     </row>
     <row r="110" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D110" s="48" t="str" cm="1">
+      <c r="D110" s="47" t="str" cm="1">
         <f t="array" ref="D110">SourceData_Swine.SourceData_Swine_NitrousOxideEFs_Variation()</f>
         <v>VARIATION ON SOURCE DATA: Added 'NIR reference column to aid lookup.</v>
       </c>
@@ -12942,13 +12974,13 @@
     </row>
     <row r="111" spans="4:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D111" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="E111" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="F111" s="33" t="s">
         <v>131</v>
-      </c>
-      <c r="E111" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="F111" s="33" t="s">
-        <v>133</v>
       </c>
       <c r="M111" s="1"/>
     </row>
@@ -13066,7 +13098,7 @@
       <c r="M121" s="1"/>
     </row>
     <row r="122" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D122" s="46" t="str" cm="1">
+      <c r="D122" s="45" t="str" cm="1">
         <f t="array" ref="D122">SourceData_Swine.SourceData_Swine_MegajoulesPerKilogramMethane_Variable()</f>
         <v>F</v>
       </c>
@@ -13074,7 +13106,7 @@
         <f t="array" ref="E122">SourceData_Swine.SourceData_Swine_MegajoulesPerKilogramMethane_Data()</f>
         <v>55.22</v>
       </c>
-      <c r="F122" s="47" t="str" cm="1">
+      <c r="F122" s="46" t="str" cm="1">
         <f t="array" ref="F122">SourceData_Swine.SourceData_Swine_MegajoulesPerKilogramMethane_Unit()</f>
         <v>MJ / kg CH4</v>
       </c>
@@ -13104,10 +13136,10 @@
     </row>
     <row r="127" spans="4:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D127" s="33" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E127" s="33" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="M127" s="1"/>
       <c r="V127" s="1"/>
@@ -14132,7 +14164,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="14">
+  <tableParts count="15">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -14147,6 +14179,7 @@
     <tablePart r:id="rId12"/>
     <tablePart r:id="rId13"/>
     <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
 </file>
@@ -14233,7 +14266,7 @@
       <c r="BM5" s="3"/>
     </row>
     <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="121" t="s">
+      <c r="A6" s="120" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="33" t="s">
@@ -14247,7 +14280,7 @@
       </c>
     </row>
     <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="120" t="str">
+      <c r="A7" s="119" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
@@ -14800,20 +14833,20 @@
     </row>
     <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
-      <c r="D59" s="48" t="str" cm="1">
+      <c r="D59" s="47" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
-      <c r="D60" s="48" t="str">
+      <c r="D60" s="47" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
-      <c r="D61" s="48" t="str">
+      <c r="D61" s="47" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
@@ -15008,32 +15041,32 @@
     </row>
     <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
-      <c r="D83" s="48" t="str" cm="1">
+      <c r="D83" s="47" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
-      <c r="D84" s="48" t="str">
+      <c r="D84" s="47" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
     <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
-      <c r="D85" s="48" t="str">
+      <c r="D85" s="47" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
     <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
-      <c r="D86" s="48" t="str">
+      <c r="D86" s="47" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
     <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
-      <c r="D87" s="48" t="str">
+      <c r="D87" s="47" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
@@ -15641,32 +15674,32 @@
     </row>
     <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
-      <c r="D99" s="47" t="str" cm="1">
+      <c r="D99" s="46" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
-      <c r="D100" s="47" t="str">
+      <c r="D100" s="46" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
     <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
-      <c r="D101" s="47" t="str">
+      <c r="D101" s="46" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
-      <c r="D102" s="47" t="str">
+      <c r="D102" s="46" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
     <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
-      <c r="D103" s="47"/>
+      <c r="D103" s="46"/>
     </row>
     <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
@@ -15687,7 +15720,7 @@
     </row>
     <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
-      <c r="D107" s="48" t="str" cm="1">
+      <c r="D107" s="47" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
@@ -15791,7 +15824,7 @@
     </row>
     <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
-      <c r="D117" s="48" t="str" cm="1">
+      <c r="D117" s="47" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra Rainfall min and Rainfall max columns to calculate zone from real rainfall data.</v>
       </c>
@@ -15937,10 +15970,10 @@
     <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
+        <v>68</v>
+      </c>
+      <c r="E134" t="s">
         <v>69</v>
-      </c>
-      <c r="E134" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -16023,7 +16056,7 @@
     </row>
     <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
-      <c r="D141" s="48" t="str" cm="1">
+      <c r="D141" s="47" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Table created based on VEERG text 'Areas are subject to leaching (i.e., in the leaching zone) when... the land is irrigated (except drip irrigation).'</v>
       </c>
@@ -16032,10 +16065,10 @@
     <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E142" s="33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="BN142" s="7"/>
     </row>
@@ -16342,7 +16375,7 @@
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
       </c>
-      <c r="E175" s="47" t="str" cm="1">
+      <c r="E175" s="46" t="str" cm="1">
         <f t="array" ref="E175">Common_SourceData.Common_SourceData_DensityOfMethane_Unit()</f>
         <v>kg/m3</v>
       </c>
@@ -16379,49 +16412,49 @@
       <c r="BP179" s="7"/>
     </row>
     <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D180" s="47" t="str" cm="1">
+      <c r="D180" s="46" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
     <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D181" s="48" t="str" cm="1">
+      <c r="D181" s="47" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
     <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D182" s="48" t="str">
+      <c r="D182" s="47" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
     <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D183" s="48" t="str">
+      <c r="D183" s="47" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
     <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D184" s="48" t="str">
+      <c r="D184" s="47" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
     <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D185" s="48" t="str">
+      <c r="D185" s="47" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
     <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="E186" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="E186" s="33" t="s">
+      <c r="F186" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F186" s="33" t="s">
+      <c r="G186" s="33" t="s">
         <v>79</v>
-      </c>
-      <c r="G186" s="33" t="s">
-        <v>80</v>
       </c>
       <c r="H186" s="33" t="s">
         <v>22</v>
@@ -16726,13 +16759,13 @@
       </c>
     </row>
     <row r="204" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D204" s="48" t="str" cm="1">
+      <c r="D204" s="47" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
     <row r="205" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D205" s="47" t="str" cm="1">
+      <c r="D205" s="46" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
@@ -16742,7 +16775,7 @@
         <v>5</v>
       </c>
       <c r="E206" s="33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="207" spans="4:8" x14ac:dyDescent="0.25">
@@ -16773,10 +16806,10 @@
     </row>
     <row r="212" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D212" s="33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E212" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="213" spans="4:5" x14ac:dyDescent="0.25">
@@ -16912,7 +16945,7 @@
       </c>
     </row>
     <row r="229" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D229" s="48" t="str" cm="1">
+      <c r="D229" s="47" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
@@ -16922,49 +16955,49 @@
         <v>39</v>
       </c>
       <c r="E231" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="F231" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="G231" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="F231" s="32" t="s">
+      <c r="H231" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="G231" s="33" t="s">
+      <c r="I231" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="H231" s="33" t="s">
+      <c r="J231" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="I231" s="33" t="s">
+      <c r="K231" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="J231" s="33" t="s">
+      <c r="L231" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="K231" s="33" t="s">
+      <c r="M231" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="L231" s="33" t="s">
+      <c r="N231" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="M231" s="33" t="s">
+      <c r="O231" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="N231" s="33" t="s">
+      <c r="P231" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="O231" s="33" t="s">
+      <c r="Q231" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="P231" s="33" t="s">
+      <c r="R231" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="Q231" s="33" t="s">
+      <c r="S231" s="33" t="s">
         <v>150</v>
-      </c>
-      <c r="R231" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="S231" s="33" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="232" spans="4:19" x14ac:dyDescent="0.25">
@@ -18240,17 +18273,17 @@
       </c>
     </row>
     <row r="256" spans="4:19" x14ac:dyDescent="0.25">
-      <c r="D256" s="47" t="str" cm="1">
+      <c r="D256" s="46" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
     <row r="257" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D257" s="33" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E257" s="33" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="258" spans="4:6" x14ac:dyDescent="0.25">
@@ -18275,31 +18308,31 @@
     </row>
     <row r="263" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D263" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="264" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D264" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="265" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D265" s="33" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E265" s="33" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F265" s="33" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="266" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D266" s="33" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E266" s="33" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F266" s="33">
         <v>5</v>
@@ -18307,10 +18340,10 @@
     </row>
     <row r="267" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D267" s="33" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E267" s="33" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F267" s="33">
         <v>4</v>
@@ -18318,10 +18351,10 @@
     </row>
     <row r="268" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D268" s="33" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E268" s="33" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F268" s="33">
         <v>3</v>
@@ -18329,10 +18362,10 @@
     </row>
     <row r="269" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D269" s="33" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E269" s="33" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F269" s="33">
         <v>2</v>
@@ -18340,10 +18373,10 @@
     </row>
     <row r="270" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D270" s="33" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E270" s="33" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F270" s="33">
         <v>1</v>
@@ -18351,26 +18384,26 @@
     </row>
     <row r="273" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D273" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="274" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D274" s="33" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E274" s="33" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F274" s="33" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="275" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D275" s="33" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E275" s="33" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F275" s="33">
         <v>5</v>
@@ -18378,10 +18411,10 @@
     </row>
     <row r="276" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D276" s="33" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E276" s="33" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F276" s="33">
         <v>4</v>
@@ -18389,10 +18422,10 @@
     </row>
     <row r="277" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D277" s="33" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E277" s="33" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F277" s="33">
         <v>3</v>
@@ -18400,10 +18433,10 @@
     </row>
     <row r="278" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D278" s="33" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E278" s="33" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F278" s="33">
         <v>2</v>
@@ -18411,10 +18444,10 @@
     </row>
     <row r="279" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D279" s="33" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E279" s="33" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F279" s="33">
         <v>1</v>
@@ -18422,26 +18455,26 @@
     </row>
     <row r="282" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D282" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="283" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D283" s="33" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E283" s="33" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F283" s="33" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="284" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D284" s="33" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E284" s="33" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F284" s="33">
         <v>5</v>
@@ -18449,10 +18482,10 @@
     </row>
     <row r="285" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D285" s="33" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E285" s="33" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F285" s="33">
         <v>4</v>
@@ -18460,10 +18493,10 @@
     </row>
     <row r="286" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D286" s="33" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E286" s="33" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F286" s="33">
         <v>3</v>
@@ -18471,10 +18504,10 @@
     </row>
     <row r="287" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D287" s="33" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E287" s="33" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F287" s="33">
         <v>2</v>
@@ -18482,10 +18515,10 @@
     </row>
     <row r="288" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D288" s="33" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E288" s="33" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F288" s="33">
         <v>1</v>
@@ -18493,26 +18526,26 @@
     </row>
     <row r="291" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D291" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="292" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D292" s="33" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E292" s="33" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F292" s="33" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="293" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D293" s="33" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E293" s="33" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F293" s="33">
         <v>5</v>
@@ -18520,10 +18553,10 @@
     </row>
     <row r="294" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D294" s="33" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E294" s="33" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F294" s="33">
         <v>4</v>
@@ -18531,10 +18564,10 @@
     </row>
     <row r="295" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D295" s="33" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E295" s="33" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F295" s="33">
         <v>3</v>
@@ -18542,10 +18575,10 @@
     </row>
     <row r="296" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D296" s="33" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E296" s="33" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F296" s="33">
         <v>2</v>
@@ -18553,10 +18586,10 @@
     </row>
     <row r="297" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D297" s="33" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E297" s="33" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F297" s="33">
         <v>1</v>
@@ -18609,11 +18642,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="e" vm="1">
+      <c r="A1" s="58" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>56</v>
+        <v>224</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -18707,13 +18740,13 @@
         <v>Site</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="33" t="s">
         <v>9</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" s="3"/>
     </row>
@@ -18834,7 +18867,7 @@
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="121" t="s">
+      <c r="A17" s="120" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="33" t="str" cm="1">
@@ -18890,9 +18923,9 @@
       <c r="G19" s="3"/>
     </row>
     <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="120" t="str">
-        <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
-        <v>Constants - Livestock</v>
+      <c r="A20" s="119" t="str">
+        <f>HYPERLINK("#'Constants - Common livestock'!A1", "Constants - Common livestock")</f>
+        <v>Constants - Common livestock</v>
       </c>
       <c r="D20" s="33" t="str" cm="1">
         <f t="array" ref="D20">Common_InputFunctions.Utility_DisplayArrayInTable(CommonLivestock_SourceData.SourceData_Livestock_Common_SymbolsMMS_Data(), Table_Data_MMSSymbols[[#Headers],[Symbol]], 0)</f>
